--- a/paper_trades/dashboard_2026-06-03.xlsx
+++ b/paper_trades/dashboard_2026-06-03.xlsx
@@ -4558,7 +4558,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>محسوب في: 2026-06-03T02:01:56</t>
+          <t>محسوب في: 2026-06-03T08:43:26</t>
         </is>
       </c>
     </row>
